--- a/docs/RequisicaodeLocal.xlsx
+++ b/docs/RequisicaodeLocal.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emerson\Documents\MBA\Projetos\weather-forecast\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1AFA35-01FF-45AD-8E98-D4824C55CE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E39F610-0F35-4A78-86FB-437BD3C4BAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{82DAF6A5-F18B-44F6-AD2C-6EE97B41B152}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82DAF6A5-F18B-44F6-AD2C-6EE97B41B152}"/>
   </bookViews>
   <sheets>
     <sheet name="Seleção de cidade para consulta" sheetId="1" r:id="rId1"/>
-    <sheet name="User location" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Weather Page</t>
   </si>
@@ -142,12 +141,6 @@
   </si>
   <si>
     <t>Retorna um dicionario com o local formatado para No padrão do App</t>
-  </si>
-  <si>
-    <t>Busca pelo user location</t>
-  </si>
-  <si>
-    <t>local = retorna_local(user_local)</t>
   </si>
 </sst>
 </file>
@@ -255,36 +248,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1146,329 +1138,6 @@
           <a:schemeClr val="accent6"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>752476</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>180976</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="2" name="Conector: Angulado 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ACD56E2-53D7-4D89-98F3-5EC6766FD471}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="16200000" flipH="1">
-          <a:off x="1452563" y="1824038"/>
-          <a:ext cx="523875" cy="552450"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>876301</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>238126</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Conector: Angulado 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59D3C66F-B743-4705-B372-83595C8BB821}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="16200000" flipH="1">
-          <a:off x="2700338" y="2681288"/>
-          <a:ext cx="523875" cy="552450"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>752476</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>180976</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="Conector: Angulado 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C32B051C-8541-4F17-95C1-52EEFDBF85DF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="16200000" flipH="1">
-          <a:off x="16959263" y="1824038"/>
-          <a:ext cx="523875" cy="552450"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>876301</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>238126</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="5" name="Conector: Angulado 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A5E554B-855D-421E-AB65-633D2812503D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="16200000" flipH="1">
-          <a:off x="18607088" y="2281238"/>
-          <a:ext cx="523875" cy="1352550"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>1114426</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>2466976</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>123826</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="Conector: Angulado 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4331424-FA09-4527-A0CB-D5B6E5FA089B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="16200000" flipH="1">
-          <a:off x="20835938" y="3186114"/>
-          <a:ext cx="523875" cy="1352550"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>1046389</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="Conector de Seta Reta 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C4F465E-B643-4927-AD13-4960E3B42763}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="23077714" y="4467225"/>
-          <a:ext cx="10886" cy="1219200"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
           <a:schemeClr val="accent6"/>
         </a:effectRef>
         <a:fontRef idx="minor">
@@ -1817,30 +1486,30 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:19" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="5"/>
+      <c r="P3" s="9"/>
     </row>
     <row r="5" spans="2:19" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="8"/>
-      <c r="N5" s="9" t="s">
+      <c r="L5" s="13"/>
+      <c r="N5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9" t="s">
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
     </row>
     <row r="6" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1848,16 +1517,16 @@
       <c r="B8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="4" t="s">
         <v>18</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="P8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1865,62 +1534,62 @@
       <c r="G9" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="L9" s="6" t="s">
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="L9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="P9" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="K10" s="10" t="s">
+      <c r="H10" s="12"/>
+      <c r="K10" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
     </row>
     <row r="12" spans="2:19" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
       <c r="P12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3" t="s">
+      <c r="Q12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
       <c r="K13" t="s">
         <v>29</v>
       </c>
-      <c r="P13" s="4" t="s">
+      <c r="P13" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="J14" s="2" t="s">
+      <c r="J14" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1931,7 +1600,7 @@
       <c r="Q16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="R16" s="3" t="s">
+      <c r="R16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1939,25 +1608,25 @@
       <c r="G17" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
     </row>
     <row r="18" spans="7:18" x14ac:dyDescent="0.25">
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K18" s="13"/>
+      <c r="K18" s="11"/>
     </row>
     <row r="19" spans="7:18" x14ac:dyDescent="0.25">
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
     </row>
     <row r="20" spans="7:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="Q20" s="4" t="s">
+      <c r="Q20" s="3" t="s">
         <v>10</v>
       </c>
       <c r="R20" s="1" t="s">
@@ -1965,7 +1634,7 @@
       </c>
     </row>
     <row r="21" spans="7:18" x14ac:dyDescent="0.25">
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="8" t="s">
         <v>32</v>
       </c>
       <c r="Q21" t="s">
@@ -1983,7 +1652,7 @@
       </c>
     </row>
     <row r="24" spans="7:18" x14ac:dyDescent="0.25">
-      <c r="J24" s="12"/>
+      <c r="J24" s="7"/>
       <c r="Q24" t="s">
         <v>14</v>
       </c>
@@ -1995,6 +1664,8 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="H9:J9"/>
     <mergeCell ref="J18:K19"/>
     <mergeCell ref="G10:H12"/>
     <mergeCell ref="H13:J13"/>
@@ -2002,130 +1673,6 @@
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="N5:P5"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="H9:J9"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D438582E-92C0-4709-8754-099149A2373C}">
-  <dimension ref="B3:R25"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
-    <col min="4" max="4" width="41.375" customWidth="1"/>
-    <col min="13" max="13" width="15.75" customWidth="1"/>
-    <col min="14" max="14" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35" customWidth="1"/>
-    <col min="16" max="16" width="35.75" customWidth="1"/>
-    <col min="17" max="17" width="23.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="N3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="5"/>
-    </row>
-    <row r="5" spans="2:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-    </row>
-    <row r="6" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="2:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" s="6"/>
-      <c r="N8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="O9" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="2:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="O13" s="4"/>
-    </row>
-    <row r="16" spans="2:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="16:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="P20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="16:17" x14ac:dyDescent="0.25">
-      <c r="P25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
